--- a/survey_templates/037_finance_policy_adoption_survey--survey_templates.xlsx
+++ b/survey_templates/037_finance_policy_adoption_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,7 +515,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>finance_policy_awareness</t>
+          <t>Finance policy awareness</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,17 +538,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>policy_implementation</t>
+          <t>policy_awareness_score</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>policy_implementation</t>
+          <t>Policy awareness score</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>challenges_encountered</t>
+          <t>policy_implementation</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>challenges_encounter</t>
+          <t>Policy implementation</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>policy_adoption_status</t>
+          <t>policy_implementation_score</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>policy_adoption_status</t>
+          <t>Policy implementation score</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>finance_policy_awareness_score</t>
+          <t>challenges_encountered</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>finance_policy_awareness_score</t>
+          <t>Challenges encountered</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>policy_implementation_score</t>
+          <t>challenges_encountered_score</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>policy_implementation_score</t>
+          <t>Challenges encountered score</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>challenges_encountered_score</t>
+          <t>policy_adoption_status</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>challenges_encounter_score</t>
+          <t>Policy adoption status</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>policy_adoption_status_score</t>
+          <t>Policy adoption status score</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,63 +699,63 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>finance_policy_awareness</t>
+          <t>question_1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>finance_policy_awareness</t>
+          <t>What is the current level of finance policy awareness among employees?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>finance_policy_awareness_score</t>
+          <t>question_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>finance_policy_awareness_score</t>
+          <t>How well is the finance policy implemented in the organization?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>policy_awareness</t>
+          <t>question_3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>policy_awareness</t>
+          <t>What are the challenges encountered during policy implementation?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,23 +768,23 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>policy_awareness_score</t>
+          <t>question_4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>policy_awareness_score</t>
+          <t>What is the status of policy adoption in the organization?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>policy_implementation</t>
+          <t>question_5</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>policy_implementation</t>
+          <t>How well is the finance policy awareness score rated?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>policy_implementation_score</t>
+          <t>question_6</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>policy_implementation_score</t>
+          <t>How well is the policy implementation score rated?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>challenges_encounter</t>
+          <t>question_7</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>challenges_encounter</t>
+          <t>What is the score for challenges encountered during policy implementation?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>challenges_encounter_score</t>
+          <t>question_8</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>challenges_encounter_score</t>
+          <t>How well is the policy adoption status score rated?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>policy_adoption_status</t>
+          <t>question_9</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>policy_adoption_status</t>
+          <t>What is the current level of finance policy awareness?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>policy_adoption_status_score</t>
+          <t>question_10</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>policy_adoption_status_score</t>
+          <t>Question 10</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -937,12 +937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -965,153 +965,306 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>policy_implementation_choices</t>
+          <t>question_1_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>very_high</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Very high</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>policy_implementation_choices</t>
+          <t>question_1_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>policy_implementation_choices</t>
+          <t>question_1_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>challenges_encountered_choices</t>
+          <t>question_1_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>challenges_encountered_choices</t>
+          <t>question_1_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>very_low</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Very low</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>challenges_encountered_choices</t>
+          <t>question_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>strongly_agree</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Strongly agree</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>policy_adoption_status_choices</t>
+          <t>question_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>somewhat_agree</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Somewhat agree</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>policy_adoption_status_choices</t>
+          <t>question_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>policy_adoption_status_choices</t>
+          <t>question_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>somewhat_disagree</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Somewhat disagree</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>question_2_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>strongly_disagree</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Strongly disagree</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>question_3_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>financial_constraints</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Financial constraints</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>question_3_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>lack_of_resources</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Lack of resources</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>question_3_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>limited_time</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Limited time</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>question_3_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>other_(please_specify)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Other (please specify)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>question_4_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>question_4_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>question_4_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>question_4_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>very_low</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Very low</t>
         </is>
       </c>
     </row>
